--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2025 год/Исламова- делопроизводитель/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2025 год/Исламова- делопроизводитель/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.92574527356</v>
+        <v>46157.93118052313</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2025 год/Исламова- делопроизводитель/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2025 год/Исламова- делопроизводитель/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93118052313</v>
+        <v>46157.9318373304</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2025 год/Исламова- делопроизводитель/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2025 год/Исламова- делопроизводитель/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.9318373304</v>
+        <v>46157.93405825733</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2025 год/Исламова- делопроизводитель/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2025 год/Исламова- делопроизводитель/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93405825733</v>
+        <v>46157.9372390842</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2025 год/Исламова- делопроизводитель/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2025 год/Исламова- делопроизводитель/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.9372390842</v>
+        <v>46158.28221697841</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2025 год/Исламова- делопроизводитель/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2025 год/Исламова- делопроизводитель/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.28221697841</v>
+        <v>46158.29702358248</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2025 год/Исламова- делопроизводитель/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2025 год/Исламова- делопроизводитель/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29702358248</v>
+        <v>46158.29821461266</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2025 год/Исламова- делопроизводитель/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2025 год/Исламова- делопроизводитель/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29821461266</v>
+        <v>46158.33392700176</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2025 год/Исламова- делопроизводитель/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2025 год/Исламова- делопроизводитель/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.33392700176</v>
+        <v>46158.36862488335</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2025 год/Исламова- делопроизводитель/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2025 год/Исламова- делопроизводитель/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.36862488335</v>
+        <v>46158.37293450662</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">
